--- a/その他/ゲームラボ/チーム表.xlsx
+++ b/その他/ゲームラボ/チーム表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_araki\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_araki\Documents\授業資料\Textbook\その他\ゲームラボ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4804AE18-C618-465C-8BD3-B1AFE825AC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51867AE-BCDD-4C68-9C05-98313D24AEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B533C5C-3A02-422D-BEEA-234A90C33CC4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>弘中雅一</t>
   </si>
@@ -48,9 +48,6 @@
     <t>吉廣貴仁</t>
   </si>
   <si>
-    <t>松尾</t>
-  </si>
-  <si>
     <t>牧山</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>本田</t>
   </si>
   <si>
-    <t>吉本</t>
-  </si>
-  <si>
     <t>川田</t>
   </si>
   <si>
@@ -79,23 +73,6 @@
   </si>
   <si>
     <t>松永健之丞</t>
-  </si>
-  <si>
-    <t>荒木（何もしない）</t>
-    <rPh sb="0" eb="2">
-      <t>アラキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ナン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>小野田（フォロー）</t>
-    <rPh sb="0" eb="3">
-      <t>オノダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Aチーム</t>
@@ -523,16 +500,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -540,56 +517,48 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -599,6 +568,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010022090CB25C089D4999E5D2062F0001F5" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="30802f330a93761ca63bdfe18fd50293">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2b8e2421-22d5-4dba-aa48-6c18bd961710" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aa3d633146aa3b014e83cbc7efabc7c3" ns2:_="">
     <xsd:import namespace="2b8e2421-22d5-4dba-aa48-6c18bd961710"/>
@@ -736,15 +714,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -752,6 +721,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73D72925-A78B-4FBC-AB02-BA5E8B3FE70A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D606326-E0F3-42F5-9664-D7FF2518F4F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -769,14 +746,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73D72925-A78B-4FBC-AB02-BA5E8B3FE70A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{144B9271-A3C3-4D8F-9542-138A97B584E2}">
   <ds:schemaRefs>
